--- a/new-stats/cherno-more.xlsx
+++ b/new-stats/cherno-more.xlsx
@@ -781,22 +781,58 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Cherno More</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Dunav Ruse</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
+      <c r="M7" t="n">
+        <v>12</v>
+      </c>
+      <c r="N7" t="n">
+        <v>5</v>
+      </c>
+      <c r="O7" t="n">
+        <v>5</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>

--- a/new-stats/cherno-more.xlsx
+++ b/new-stats/cherno-more.xlsx
@@ -835,22 +835,58 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CSKA Sofia</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Cherno More</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
+      <c r="M8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N8" t="n">
+        <v>7</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3</v>
+      </c>
+      <c r="P8" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>

--- a/new-stats/cherno-more.xlsx
+++ b/new-stats/cherno-more.xlsx
@@ -889,22 +889,58 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>06/09/2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Lok. Plovdiv</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Cherno More</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
+      <c r="M9" t="n">
+        <v>12</v>
+      </c>
+      <c r="N9" t="n">
+        <v>8</v>
+      </c>
+      <c r="O9" t="n">
+        <v>6</v>
+      </c>
+      <c r="P9" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>

--- a/new-stats/cherno-more.xlsx
+++ b/new-stats/cherno-more.xlsx
@@ -943,22 +943,58 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Cherno More</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Lok. Sofia</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2</v>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
+      <c r="M10" t="n">
+        <v>12</v>
+      </c>
+      <c r="N10" t="n">
+        <v>8</v>
+      </c>
+      <c r="O10" t="n">
+        <v>4</v>
+      </c>
+      <c r="P10" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>

--- a/new-stats/cherno-more.xlsx
+++ b/new-stats/cherno-more.xlsx
@@ -997,22 +997,58 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>19/09/2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Arda</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Cherno More</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
+      <c r="M11" t="n">
+        <v>9</v>
+      </c>
+      <c r="N11" t="n">
+        <v>10</v>
+      </c>
+      <c r="O11" t="n">
+        <v>5</v>
+      </c>
+      <c r="P11" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>

--- a/new-stats/cherno-more.xlsx
+++ b/new-stats/cherno-more.xlsx
@@ -1051,22 +1051,58 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>11/10/2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Cherno More</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Levski</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
+      <c r="M12" t="n">
+        <v>7</v>
+      </c>
+      <c r="N12" t="n">
+        <v>12</v>
+      </c>
+      <c r="O12" t="n">
+        <v>4</v>
+      </c>
+      <c r="P12" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>

--- a/new-stats/cherno-more.xlsx
+++ b/new-stats/cherno-more.xlsx
@@ -1105,22 +1105,58 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>27/10/2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Cherno More</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Septemvri Sofia</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
+      <c r="M13" t="n">
+        <v>13</v>
+      </c>
+      <c r="N13" t="n">
+        <v>7</v>
+      </c>
+      <c r="O13" t="n">
+        <v>3</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
